--- a/Result/profitability/5443.xlsx
+++ b/Result/profitability/5443.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>0.15</v>
       </c>
       <c r="M2" t="n">
-        <v>0.4737500000000001</v>
+        <v>0.52625</v>
       </c>
       <c r="N2" t="n">
-        <v>32.1525</v>
+        <v>32.95625</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -780,10 +780,10 @@
         <v>0.22</v>
       </c>
       <c r="M3" t="n">
-        <v>0.42</v>
+        <v>0.5275</v>
       </c>
       <c r="N3" t="n">
-        <v>31.015</v>
+        <v>32.7325</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -899,13 +899,13 @@
         <v>0.42</v>
       </c>
       <c r="M4" t="n">
-        <v>0.44625</v>
+        <v>0.52375</v>
       </c>
       <c r="N4" t="n">
-        <v>31.45375</v>
+        <v>31.15</v>
       </c>
       <c r="O4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P4" t="n">
         <v>0</v>
@@ -1018,10 +1018,10 @@
         <v>-0.03</v>
       </c>
       <c r="M5" t="n">
-        <v>0.38625</v>
+        <v>0.385</v>
       </c>
       <c r="N5" t="n">
-        <v>28.75625</v>
+        <v>28.64</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>-0.28</v>
       </c>
       <c r="M6" t="n">
-        <v>0.21625</v>
+        <v>0.295</v>
       </c>
       <c r="N6" t="n">
-        <v>26.45125</v>
+        <v>26.61</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1264,10 +1264,10 @@
         <v>-1.12</v>
       </c>
       <c r="M7" t="n">
-        <v>0.02125000000000002</v>
+        <v>0.07750000000000001</v>
       </c>
       <c r="N7" t="n">
-        <v>22.2775</v>
+        <v>22.57625</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1391,10 +1391,10 @@
         <v>-0.15</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.075</v>
+        <v>0.03500000000000002</v>
       </c>
       <c r="N8" t="n">
-        <v>20.6225</v>
+        <v>20.2525</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -9826,6 +9826,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>5443</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>1144</v>
+      </c>
+      <c r="D75" t="n">
+        <v>739</v>
+      </c>
+      <c r="E75" t="n">
+        <v>405</v>
+      </c>
+      <c r="F75" t="n">
+        <v>35.38</v>
+      </c>
+      <c r="G75" t="n">
+        <v>22</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>1.89%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>223</v>
+      </c>
+      <c r="J75" t="n">
+        <v>244</v>
+      </c>
+      <c r="K75" t="n">
+        <v>173</v>
+      </c>
+      <c r="L75" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="M75" t="n">
+        <v>0.5887500000000001</v>
+      </c>
+      <c r="N75" t="n">
+        <v>33.19125</v>
+      </c>
+      <c r="O75" t="n">
+        <v>1</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>1</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>1</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>0.8800000000000001</v>
+      </c>
+      <c r="X75" t="n">
+        <v>4.631578947368421</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>-2.960000000000001</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>-0.07720396452790823</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>-0.01000000000000001</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>-0.0092592592592593</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>-0.9299999999999997</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>-0.02561277884880198</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS衰退 / 毛利率衰退</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
